--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7892991-8CF9-4092-B305-D32F1D32DCBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F40DF4-64E1-4486-8A1C-ECFA39A4AB74}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -54,28 +54,28 @@
     <t>Title__c</t>
   </si>
   <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Automation Test Description</t>
+  </si>
+  <si>
+    <t>Unit__c</t>
+  </si>
+  <si>
+    <t>Dollar ($)</t>
+  </si>
+  <si>
+    <t>Orientation__c</t>
+  </si>
+  <si>
+    <t>Increase</t>
+  </si>
+  <si>
+    <t>Economic Development</t>
+  </si>
+  <si>
     <t>Automation KPI Regression</t>
-  </si>
-  <si>
-    <t>Description__c</t>
-  </si>
-  <si>
-    <t>Automation Test Description</t>
-  </si>
-  <si>
-    <t>Unit__c</t>
-  </si>
-  <si>
-    <t>Dollar ($)</t>
-  </si>
-  <si>
-    <t>Orientation__c</t>
-  </si>
-  <si>
-    <t>Increase</t>
-  </si>
-  <si>
-    <t>Economic Development</t>
   </si>
 </sst>
 </file>
@@ -431,7 +431,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -464,7 +464,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -472,10 +472,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -494,10 +494,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -533,7 +533,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F40DF4-64E1-4486-8A1C-ECFA39A4AB74}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2208FAD9-A7BA-4099-B1AA-B06B1A5D9DBE}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <t>Economic Development</t>
   </si>
   <si>
-    <t>Automation KPI Regression</t>
+    <t>Automation KPI</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2208FAD9-A7BA-4099-B1AA-B06B1A5D9DBE}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D7AB79-B751-4E86-94A7-FD7B9A0F58A7}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <t>Economic Development</t>
   </si>
   <si>
-    <t>Automation KPI</t>
+    <t>Execution KPI for Automation</t>
   </si>
 </sst>
 </file>
@@ -428,13 +428,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -456,7 +456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -467,7 +467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -478,7 +478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -489,7 +489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -502,19 +502,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -525,7 +526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D7AB79-B751-4E86-94A7-FD7B9A0F58A7}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97A4087-5D2A-4D7D-BDAF-A3CAAF877C51}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="3612" yWindow="2448" windowWidth="17280" windowHeight="8964" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <t>Economic Development</t>
   </si>
   <si>
-    <t>Execution KPI for Automation</t>
+    <t>KPI for Automation Testing</t>
   </si>
 </sst>
 </file>
@@ -428,13 +428,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -456,7 +456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -467,7 +467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -478,7 +478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -489,7 +489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -509,13 +509,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97A4087-5D2A-4D7D-BDAF-A3CAAF877C51}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E683456-B88F-4B9D-BB67-C1692D7245E9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3612" yWindow="2448" windowWidth="17280" windowHeight="8964" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <t>Economic Development</t>
   </si>
   <si>
-    <t>KPI for Automation Testing</t>
+    <t>Automation Execution KPI for Regression</t>
   </si>
 </sst>
 </file>
@@ -428,13 +428,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -456,7 +456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -467,7 +467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -478,7 +478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -489,7 +489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -509,13 +509,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E683456-B88F-4B9D-BB67-C1692D7245E9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D07D9E-D14F-41E3-958D-D203A0706F93}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <t>Economic Development</t>
   </si>
   <si>
-    <t>Automation Execution KPI for Regression</t>
+    <t>Automation Execution KPI</t>
   </si>
 </sst>
 </file>
@@ -428,13 +428,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -456,7 +456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -467,7 +467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -478,7 +478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -489,7 +489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -509,13 +509,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0F02D2-F2BA-48AF-B417-3F08C56D9EFF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CFF1B4-C66C-44EA-8531-5C3B45CEF9FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
@@ -82,19 +82,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF00396B"/>
-      <name val="Helvetica"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,9 +111,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,7 +463,7 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
     </row>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CFF1B4-C66C-44EA-8531-5C3B45CEF9FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E82F68F-0744-4AD1-957D-8A358A1DF0BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <t>Economic Development</t>
   </si>
   <si>
-    <t>Automation Execution KPI</t>
+    <t>Automation Runtime KPI</t>
   </si>
 </sst>
 </file>
@@ -428,13 +428,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -456,7 +456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -467,7 +467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -478,7 +478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -489,7 +489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -509,13 +509,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductClassic\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E82F68F-0744-4AD1-957D-8A358A1DF0BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E432B9C9-64F2-4732-A5DC-36C383575939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -428,13 +428,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -456,7 +456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -467,7 +467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -478,7 +478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -489,7 +489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -509,13 +509,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
